--- a/data_clean/metadata.xlsx
+++ b/data_clean/metadata.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -954,6 +954,186 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Befolkningsvekst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C_x0005_rlig vekst i befolkningen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Beregnet</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Befolkning</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Prosent</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>C_x0005_rlig</t>
+        </is>
+      </c>
+      <c r="H13">
+        <v>1736</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>create_derived_variables</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Beregnet som (Befolkning / lag(Befolkning) - 1) * 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Reallonnsvekst</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LC8nnsvekst minus inflasjon</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Beregnet</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Lonnvekst og Inflasjon</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Prosent</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>C_x0005_rlig</t>
+        </is>
+      </c>
+      <c r="H14">
+        <v>1971</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>create_derived_variables</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Beregnet som Lonnvekst - Inflasjon</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Arbeidsstyrkeandel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arbeidsstyrken som andel av befolkningen</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Beregnet</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Arbeidsstyrke og Befolkning</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Prosent</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>C_x0005_rlig</t>
+        </is>
+      </c>
+      <c r="H15">
+        <v>1972</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>create_derived_variables</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Beregnet som Arbeidsstyrke / Befolkning * 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Arbledige_andel_arbeidsstyrke_NAV</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Registrerte arbeidsledige som andel av arbeidsstyrken</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Beregnet</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Arbledige_NAV og Arbeidsstyrke</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Prosent</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>C_x0005_rlig</t>
+        </is>
+      </c>
+      <c r="H16">
+        <v>1972</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>create_derived_variables</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Beregnet som Arbledige_NAV / Arbeidsstyrke * 100</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
